--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T11:53:23+00:00</t>
+    <t>2026-09-18T08:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:26:19+00:00</t>
+    <t>2026-09-24T07:33:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-24T07:33:45+00:00</t>
+    <t>2026-09-30T20:06:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T20:06:50+00:00</t>
+    <t>2026-10-01T08:49:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T08:49:37+00:00</t>
+    <t>2026-10-01T13:34:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-procedure-document.xlsx
+++ b/main/ig/StructureDefinition-fr-procedure-document.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2747" uniqueCount="476">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T13:34:48+00:00</t>
+    <t>2026-10-05T07:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -491,127 +491,134 @@
     <t>Procedure.extension.id</t>
   </si>
   <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Procedure.extension:approachBodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.extension.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Procedure.extension:approachBodySite.url</t>
+  </si>
+  <si>
+    <t>Procedure.extension.url</t>
+  </si>
+  <si>
+    <t>identifies the meaning of the extension</t>
+  </si>
+  <si>
+    <t>Source of the definition for the extension code - a logical name or a URL.</t>
+  </si>
+  <si>
+    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/StructureDefinition/procedure-approachBodyStructure</t>
+  </si>
+  <si>
+    <t>Extension.url</t>
+  </si>
+  <si>
+    <t>Procedure.extension:approachBodySite.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-body-structure-document|0.1.0)
+</t>
+  </si>
+  <si>
+    <t>Value of extension</t>
+  </si>
+  <si>
+    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R5/extensibility.html) for a list).</t>
+  </si>
+  <si>
+    <t>Extension.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ext-1
+</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant</t>
+  </si>
+  <si>
+    <t>participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
+</t>
+  </si>
+  <si>
+    <t>Participant à l'acte</t>
+  </si>
+  <si>
+    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Procedure.extension:approachBodySite.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension:approachBodySite.url</t>
-  </si>
-  <si>
-    <t>Procedure.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/procedure-approachBodyStructure</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>Procedure.extension:approachBodySite.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-body-structure-document|0.1.0)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
+    <t>Procedure.extension:participant.extension</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant.extension:type</t>
+  </si>
+  <si>
+    <t>type</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant.extension:type.id</t>
+  </si>
+  <si>
+    <t>Procedure.extension.extension.id</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant.extension:type.extension</t>
+  </si>
+  <si>
+    <t>Procedure.extension.extension.extension</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant.extension:type.url</t>
+  </si>
+  <si>
+    <t>Procedure.extension.extension.url</t>
+  </si>
+  <si>
+    <t>Procedure.extension:participant.extension:type.value[x]</t>
+  </si>
+  <si>
+    <t>Procedure.extension.extension.value[x]</t>
   </si>
   <si>
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant</t>
-  </si>
-  <si>
-    <t>participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/document-core/StructureDefinition/fr-actor-extension|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Participant à l'acte</t>
-  </si>
-  <si>
-    <t>Extension permettant de représenter un acteur impliqué dans le document avec son type et sa référence.</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant.id</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant.extension</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant.extension:type</t>
-  </si>
-  <si>
-    <t>type</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant.extension:type.id</t>
-  </si>
-  <si>
-    <t>Procedure.extension.extension.id</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant.extension:type.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension.extension.extension</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant.extension:type.url</t>
-  </si>
-  <si>
-    <t>Procedure.extension.extension.url</t>
-  </si>
-  <si>
-    <t>Procedure.extension:participant.extension:type.value[x]</t>
-  </si>
-  <si>
-    <t>Procedure.extension.extension.value[x]</t>
   </si>
   <si>
     <t>PART</t>
@@ -3090,7 +3097,7 @@
         <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>138</v>
@@ -3136,13 +3143,13 @@
         <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -3193,7 +3200,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3202,7 +3209,7 @@
         <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>144</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>77</v>
@@ -3211,7 +3218,7 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>77</v>
@@ -3222,10 +3229,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="B13" t="s" s="2">
         <v>157</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>158</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3296,7 +3303,7 @@
         <v>135</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
@@ -3305,7 +3312,7 @@
         <v>136</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3334,10 +3341,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B14" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="B14" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3363,13 +3370,13 @@
         <v>101</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3377,49 +3384,49 @@
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="S14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>166</v>
-      </c>
-      <c r="S14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>87</v>
@@ -3448,10 +3455,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="B15" t="s" s="2">
         <v>168</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>169</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3474,13 +3481,13 @@
         <v>77</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3531,7 +3538,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3540,7 +3547,7 @@
         <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="AJ15" t="s" s="2">
         <v>99</v>
@@ -3700,13 +3707,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3757,7 +3764,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3775,7 +3782,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3786,10 +3793,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3797,7 +3804,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>79</v>
@@ -3860,7 +3867,7 @@
         <v>135</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
@@ -3869,7 +3876,7 @@
         <v>136</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3898,13 +3905,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>77</v>
@@ -3983,7 +3990,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4012,10 +4019,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4038,13 +4045,13 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4095,7 +4102,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4113,7 +4120,7 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -4124,10 +4131,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4198,7 +4205,7 @@
         <v>135</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
@@ -4207,7 +4214,7 @@
         <v>136</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4236,10 +4243,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4265,13 +4272,13 @@
         <v>101</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M22" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4279,7 +4286,7 @@
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>77</v>
@@ -4321,7 +4328,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>87</v>
@@ -4350,10 +4357,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4379,10 +4386,10 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4394,7 +4401,7 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>77</v>
@@ -4409,11 +4416,11 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y23" s="2"/>
       <c r="Z23" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4431,7 +4438,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4460,13 +4467,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>77</v>
@@ -4491,7 +4498,7 @@
         <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M24" t="s" s="2">
         <v>134</v>
@@ -4545,7 +4552,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4574,10 +4581,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4600,13 +4607,13 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4657,7 +4664,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4675,7 +4682,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4686,10 +4693,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4760,7 +4767,7 @@
         <v>135</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>77</v>
@@ -4769,7 +4776,7 @@
         <v>136</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4798,10 +4805,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4827,13 +4834,13 @@
         <v>101</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4841,7 +4848,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>77</v>
@@ -4883,7 +4890,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>87</v>
@@ -4912,10 +4919,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4938,13 +4945,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4995,7 +5002,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5024,13 +5031,13 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C29" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D29" t="s" s="2">
         <v>77</v>
@@ -5109,7 +5116,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5138,10 +5145,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5164,13 +5171,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L30" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5221,7 +5228,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5239,7 +5246,7 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
@@ -5250,10 +5257,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5324,7 +5331,7 @@
         <v>135</v>
       </c>
       <c r="AC31" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="AD31" t="s" s="2">
         <v>77</v>
@@ -5333,7 +5340,7 @@
         <v>136</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5362,10 +5369,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5391,13 +5398,13 @@
         <v>101</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5405,7 +5412,7 @@
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>77</v>
@@ -5447,7 +5454,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>87</v>
@@ -5476,10 +5483,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5502,13 +5509,13 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5559,7 +5566,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5588,10 +5595,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5617,13 +5624,13 @@
         <v>101</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>164</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>165</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5631,7 +5638,7 @@
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>77</v>
@@ -5673,7 +5680,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>87</v>
@@ -5702,10 +5709,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5728,13 +5735,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>172</v>
+        <v>193</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5785,7 +5792,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5814,13 +5821,13 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B36" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C36" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D36" t="s" s="2">
         <v>77</v>
@@ -5842,13 +5849,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5928,14 +5935,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -5957,16 +5964,16 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6015,7 +6022,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6044,10 +6051,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6070,19 +6077,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6131,7 +6138,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6146,24 +6153,24 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6186,13 +6193,13 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6243,7 +6250,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6258,10 +6265,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6272,10 +6279,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6301,13 +6308,13 @@
         <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6357,7 +6364,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6372,10 +6379,10 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6386,14 +6393,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6412,13 +6419,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6469,7 +6476,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6484,10 +6491,10 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6498,14 +6505,14 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6524,16 +6531,16 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6583,7 +6590,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6598,10 +6605,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6612,10 +6619,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6641,13 +6648,13 @@
         <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6673,13 +6680,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6697,7 +6704,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>87</v>
@@ -6712,13 +6719,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6726,14 +6733,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6752,16 +6759,16 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6787,13 +6794,13 @@
         <v>77</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>77</v>
@@ -6811,7 +6818,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6826,10 +6833,10 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
@@ -6840,10 +6847,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6866,13 +6873,13 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6899,13 +6906,13 @@
         <v>77</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>77</v>
@@ -6923,7 +6930,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6941,10 +6948,10 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -6952,14 +6959,14 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6978,19 +6985,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7019,7 +7026,7 @@
       </c>
       <c r="Y46" s="2"/>
       <c r="Z46" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>77</v>
@@ -7037,7 +7044,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7052,28 +7059,28 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7092,13 +7099,13 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7149,7 +7156,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>87</v>
@@ -7164,24 +7171,24 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7204,16 +7211,16 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -7263,7 +7270,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7278,24 +7285,24 @@
         <v>99</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7318,16 +7325,16 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7377,7 +7384,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7392,24 +7399,24 @@
         <v>99</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7432,13 +7439,13 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7489,7 +7496,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7507,10 +7514,10 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7518,10 +7525,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7544,13 +7551,13 @@
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7601,7 +7608,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7619,10 +7626,10 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7630,10 +7637,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7656,13 +7663,13 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7713,7 +7720,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7728,10 +7735,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -7742,10 +7749,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7768,13 +7775,13 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7825,7 +7832,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7843,7 +7850,7 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -7854,14 +7861,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -7883,13 +7890,13 @@
         <v>132</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -7939,7 +7946,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7957,7 +7964,7 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -7968,14 +7975,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -7997,16 +8004,16 @@
         <v>132</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8055,7 +8062,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8084,10 +8091,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8110,17 +8117,17 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8145,13 +8152,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8169,7 +8176,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8184,24 +8191,24 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8224,17 +8231,17 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8283,7 +8290,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>87</v>
@@ -8298,24 +8305,24 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8338,17 +8345,17 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8397,7 +8404,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8415,7 +8422,7 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8426,10 +8433,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8452,17 +8459,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8511,7 +8518,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8529,10 +8536,10 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8540,10 +8547,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8566,16 +8573,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -8601,13 +8608,13 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>77</v>
@@ -8625,7 +8632,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8640,13 +8647,13 @@
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8654,10 +8661,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8680,16 +8687,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8739,7 +8746,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8754,13 +8761,13 @@
         <v>99</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8768,10 +8775,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8794,16 +8801,16 @@
         <v>88</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -8829,11 +8836,11 @@
         <v>77</v>
       </c>
       <c r="X62" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="Y62" s="2"/>
       <c r="Z62" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AA62" t="s" s="2">
         <v>77</v>
@@ -8851,7 +8858,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8869,21 +8876,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8906,16 +8913,16 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8941,13 +8948,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -8965,7 +8972,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -8983,7 +8990,7 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
@@ -8994,10 +9001,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9020,16 +9027,16 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9079,7 +9086,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9097,7 +9104,7 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9108,10 +9115,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9134,16 +9141,16 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9169,13 +9176,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9193,7 +9200,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9211,7 +9218,7 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9222,10 +9229,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9248,17 +9255,17 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
@@ -9307,7 +9314,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9325,7 +9332,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9336,10 +9343,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9362,13 +9369,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9395,13 +9402,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9419,7 +9426,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9437,7 +9444,7 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9448,10 +9455,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9474,13 +9481,13 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9531,7 +9538,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9546,24 +9553,24 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9586,13 +9593,13 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9643,7 +9650,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9661,7 +9668,7 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
@@ -9672,10 +9679,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9698,13 +9705,13 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="L70" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="L70" t="s" s="2">
+      <c r="M70" t="s" s="2">
         <v>153</v>
-      </c>
-      <c r="M70" t="s" s="2">
-        <v>154</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -9755,7 +9762,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9773,7 +9780,7 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
@@ -9784,14 +9791,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -9813,13 +9820,13 @@
         <v>132</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9869,7 +9876,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9887,7 +9894,7 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
@@ -9898,14 +9905,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -9927,16 +9934,16 @@
         <v>132</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -9985,7 +9992,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10014,10 +10021,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10040,13 +10047,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10076,10 +10083,10 @@
         <v>111</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>77</v>
@@ -10097,7 +10104,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10115,7 +10122,7 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
@@ -10126,10 +10133,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10152,13 +10159,13 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10209,7 +10216,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>87</v>
@@ -10227,7 +10234,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10238,10 +10245,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10264,19 +10271,19 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -10325,7 +10332,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10343,7 +10350,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10354,10 +10361,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10380,16 +10387,16 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10415,13 +10422,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -10439,7 +10446,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10457,7 +10464,7 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
